--- a/capston/ExcelFile/LoginData.xlsx
+++ b/capston/ExcelFile/LoginData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Renuka/SA2410010/SA2410010_Maven_Project/ExcelFiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jim\eclipse-workspace\SA2411063\capston\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0A3329-2E00-CD45-A473-AD5A7D85984E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F044C783-A351-4D77-8558-8615ABBF5E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6560" yWindow="2840" windowWidth="20500" windowHeight="13220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="15120" windowHeight="8700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login Data" sheetId="1" r:id="rId1"/>
@@ -20,18 +20,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>nitin</t>
-  </si>
-  <si>
-    <t>gupta</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Admin</t>
   </si>
   <si>
     <t>admin123</t>
+  </si>
+  <si>
+    <t>priya</t>
+  </si>
+  <si>
+    <t>priya1</t>
+  </si>
+  <si>
+    <t>priya123</t>
+  </si>
+  <si>
+    <t>ppppppp</t>
+  </si>
+  <si>
+    <t>pppppp1</t>
+  </si>
+  <si>
+    <t>asdafaf</t>
+  </si>
+  <si>
+    <t>asd435</t>
   </si>
 </sst>
 </file>
@@ -349,10 +364,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -360,12 +375,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/capston/ExcelFile/LoginData.xlsx
+++ b/capston/ExcelFile/LoginData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jim\eclipse-workspace\SA2411063\capston\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F044C783-A351-4D77-8558-8615ABBF5E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482E7792-ECCF-4681-BFDE-6A9AC98D5465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="15120" windowHeight="8700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="732" yWindow="732" windowWidth="15120" windowHeight="8700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t>Admin</t>
   </si>
@@ -37,16 +37,10 @@
     <t>priya123</t>
   </si>
   <si>
-    <t>ppppppp</t>
-  </si>
-  <si>
-    <t>pppppp1</t>
-  </si>
-  <si>
-    <t>asdafaf</t>
-  </si>
-  <si>
-    <t>asd435</t>
+    <t>12345w</t>
+  </si>
+  <si>
+    <t>adminnn</t>
   </si>
 </sst>
 </file>
@@ -372,15 +366,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -401,10 +395,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
